--- a/data/trans_camb/P38A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,85</t>
+          <t>-4,29; 1,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,78</t>
+          <t>-3,85; 2,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,38</t>
+          <t>-1,82; 2,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,18</t>
+          <t>-2,36; 2,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,17</t>
+          <t>-1,93; 1,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,61</t>
+          <t>-1,91; 1,75</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,06</t>
+          <t>-4,61; 2,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,12</t>
+          <t>-4,19; 2,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,55</t>
+          <t>-1,93; 2,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,35</t>
+          <t>-2,49; 2,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,25</t>
+          <t>-2,07; 1,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,75</t>
+          <t>-2,04; 1,91</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,33</t>
+          <t>-2,74; 2,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,45; -0,07</t>
+          <t>-32,2; -0,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,87</t>
+          <t>-0,67; 3,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 3,53</t>
+          <t>-9,46; 3,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,39</t>
+          <t>-1,02; 2,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 0,97</t>
+          <t>-20,27; 0,3</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,87</t>
+          <t>-3,31; 2,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,28; -0,08</t>
+          <t>-39,64; -0,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 4,53</t>
+          <t>-0,78; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 4,09</t>
+          <t>-10,86; 4,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,88</t>
+          <t>-1,2; 3,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 1,17</t>
+          <t>-24,17; 0,35</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,92; -1,06</t>
+          <t>-9,67; -0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 2,63</t>
+          <t>-6,66; 2,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,94</t>
+          <t>-5,16; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,19</t>
+          <t>-2,69; 5,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; -0,02</t>
+          <t>-6,0; -0,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,24</t>
+          <t>-3,38; 2,76</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -1,19</t>
+          <t>-10,56; -1,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,95</t>
+          <t>-7,31; 2,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 3,36</t>
+          <t>-5,62; 4,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 5,94</t>
+          <t>-2,95; 5,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -0,03</t>
+          <t>-6,59; -0,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,54</t>
+          <t>-3,73; 3,12</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,2</t>
+          <t>-3,5; 0,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,22; -1,0</t>
+          <t>-24,94; -1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,8</t>
+          <t>-1,27; 1,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 1,18</t>
+          <t>-7,27; 1,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,43</t>
+          <t>-1,86; 0,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -0,63</t>
+          <t>-15,28; -0,68</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,24</t>
+          <t>-4,05; 0,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -1,18</t>
+          <t>-29,33; -1,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,02</t>
+          <t>-1,41; 1,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 1,31</t>
+          <t>-8,07; 1,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,49</t>
+          <t>-2,1; 0,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,9; -0,71</t>
+          <t>-17,44; -0,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P38A-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-1,11</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,95</t>
+          <t>-4,1; 1,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,61</t>
+          <t>-6,42; 0,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,06</t>
+          <t>-1,66; 2,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,17</t>
+          <t>-2,13; 1,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,52</t>
+          <t>-2,11; 1,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,75</t>
+          <t>-3,25; 0,78</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0,35%</t>
+          <t>-2,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>-0,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,03%</t>
+          <t>-1,19%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 2,2</t>
+          <t>-4,44; 1,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 2,9</t>
+          <t>-7,05; 0,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,22</t>
+          <t>-1,74; 2,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,31</t>
+          <t>-2,25; 1,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,65</t>
+          <t>-2,25; 1,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,91</t>
+          <t>-3,47; 0,88</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-9,56</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>-1,17</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,19</t>
+          <t>-3,01; 2,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-32,2; -0,05</t>
+          <t>-4,86; 0,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,74</t>
+          <t>-0,72; 3,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 3,69</t>
+          <t>-3,03; 1,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,55</t>
+          <t>-0,94; 2,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 0,3</t>
+          <t>-3,12; 0,74</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-11,74%</t>
+          <t>-2,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,83%</t>
+          <t>-0,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,07%</t>
+          <t>-1,39%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,74</t>
+          <t>-3,63; 2,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,64; -0,05</t>
+          <t>-5,89; 1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,42</t>
+          <t>-0,8; 4,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 4,3</t>
+          <t>-3,44; 1,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,06</t>
+          <t>-1,11; 2,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 0,35</t>
+          <t>-3,69; 0,88</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,67; -0,99</t>
+          <t>-9,9; -1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 2,32</t>
+          <t>-5,17; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,59</t>
+          <t>-5,04; 3,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,08</t>
+          <t>-2,62; 5,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,14</t>
+          <t>-6,29; -0,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,76</t>
+          <t>-2,71; 2,58</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-2,15%</t>
+          <t>-1,63%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0,45%</t>
+          <t>-0,14%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -1,25</t>
+          <t>-10,75; -1,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 2,6</t>
+          <t>-5,64; 3,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 4,15</t>
+          <t>-5,54; 4,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,9</t>
+          <t>-2,84; 5,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -0,18</t>
+          <t>-6,96; -0,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,12</t>
+          <t>-2,95; 2,93</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,41</t>
+          <t>-1,82</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,11</t>
+          <t>-3,6; 0,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,94; -1,07</t>
+          <t>-4,66; -0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,64</t>
+          <t>-1,36; 1,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 1,06</t>
+          <t>-2,68; 0,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,42</t>
+          <t>-1,92; 0,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -0,68</t>
+          <t>-3,1; -0,53</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-8,94%</t>
+          <t>-2,98%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,57%</t>
+          <t>-1,3%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,04%</t>
+          <t>-2,07%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,12</t>
+          <t>-4,15; 0,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,33; -1,27</t>
+          <t>-5,4; -0,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,84</t>
+          <t>-1,5; 1,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,19</t>
+          <t>-2,97; 0,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,48</t>
+          <t>-2,2; 0,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -0,78</t>
+          <t>-3,52; -0,6</t>
         </is>
       </c>
     </row>
